--- a/backend/Logs/API_Logs_20250801_PENDING_1.xlsx
+++ b/backend/Logs/API_Logs_20250801_PENDING_1.xlsx
@@ -6305,22 +6305,253 @@
     <x:t>{"data":{"id":5,"title":"Task 6","description":null,"priority_level":{"name":"Medium","color":"#d1b529"},"status":{"name":"Open","color":"#d1b529"},"category":{"name":"Learn &gt; Career","icon":"\uD83D\uDCDA"},"taskOnDate":"2025-11-23T00:00:00","startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T11:12:04.810364","updatedAt":"2025-11-24T11:19:33.093255","estimatedHours":null,"priority_order":1,"subtasks":[{"id":7,"title":"tl1 1","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":"2025-11-23T00:00:00","startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T11:12:38.408176","updatedAt":"2025-11-24T11:18:11.866516","estimatedHours":0.00,"priority_order":1,"subtasks":[{"id":2,"title":"tl2 1","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":"2025-11-23T00:00:00","startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T11:13:22.766148","updatedAt":"2025-11-24T11:18:11.815897","estimatedHours":0.00,"priority_order":1,"subtasks":[],"parentId":"7","level":2,"isExpanded":false,"completed":false,"important":false}],"parentId":"5","level":1,"isExpanded":false,"completed":false,"important":false},{"id":8,"title":"tl1 2","description":"","status":{"name":"Completed","color":"#08af24"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":"2025-11-23T00:00:00","startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T11:12:47.085519","updatedAt":"2025-11-24T11:17:36.541605","estimatedHours":null,"priority_order":2,"subtasks":[],"parentId":"5","level":1,"isExpanded":false,"completed":true,"important":false}],"isExpanded":false,"remarks":null,"urls":[{"id":23,"label":"C# - Reddit","url":"https://www.reddit.com/r/csharp/comments/1hbsihw/need_a_beginnerfriendly_roadmap_for_learning_c/","credentials":[{"id":9,"provider":"G Mail","credential_name":"my main gmail acc","credential_id":"noushadhrr@gmail.com"},{"id":10,"provider":"G Mail","credential_name":"my one of old gmail","credential_id":"mohammedhrr92@gmail.com"}]}],"important":false,"completed":false,"periodic_task":null},"message":"Main task updated successfully","success":true}</x:t>
   </x:si>
   <x:si>
-    <x:t>22:48:40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"email":"admin@omniplanner.com","password":"admin123","rememberMe":false}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22:49:33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22:50:02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"data":{"token":"eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1laWRlbnRpZmllciI6IjEiLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9lbWFpbGFkZHJlc3MiOiJhZG1pbkBvbW5pcGxhbm5lci5jb20iLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1lIjoiYWRtaW4iLCJqdGkiOiI2NTc2NjM0Ny1jMThhLTQxN2ItODUyZi1hYWJkNjQ2YjRjMGUiLCJodHRwOi8vc2NoZW1hcy5taWNyb3NvZnQuY29tL3dzLzIwMDgvMDYvaWRlbnRpdHkvY2xhaW1zL3JvbGUiOiJTdXBlciBBZG1pbiIsInBlcm1pc3Npb24iOlsiYnVkZ2V0LmNyZWF0ZSIsImJ1ZGdldC5kZWxldGUiLCJidWRnZXQuZWRpdCIsImJ1ZGdldC52aWV3IiwiY2F0ZWdvcmllcy5jcmVhdGUiLCJjYXRlZ29yaWVzLmRlbGV0ZSIsImNhdGVnb3JpZXMuZWRpdCIsImNhdGVnb3JpZXMudmlldyIsImNyZWRlbnRpYWxzLmNyZWF0ZSIsImNyZWRlbnRpYWxzLmRlbGV0ZSIsImNyZWRlbnRpYWxzLmVkaXQiLCJjcmVkZW50aWFscy52aWV3Iiwibm90ZXMuY3JlYXRlIiwibm90ZXMuZGVsZXRlIiwibm90ZXMuZWRpdCIsIm5vdGVzLnZpZXciLCJwZXJtaXNzaW9ucy5tYW5hZ2UiLCJwZXJtaXNzaW9ucy52aWV3IiwicHJpb3JpdGllcy5jcmVhdGUiLCJwcmlvcml0aWVzLmRlbGV0ZSIsInByaW9yaXRpZXMuZWRpdCIsInByaW9yaXRpZXMudmlldyIsInJvbGVzLmNyZWF0ZSIsInJvbGVzLmRlbGV0ZSIsInJvbGVzLmVkaXQiLCJyb2xlcy52aWV3Iiwic2V0dGluZ3MubWFuYWdlIiwic2V0dGluZ3MudmlldyIsInN0YXR1c2VzLmNyZWF0ZSIsInN0YXR1c2VzLmRlbGV0ZSIsInN0YXR1c2VzLmVkaXQiLCJzdGF0dXNlcy52aWV3IiwidGFza3MuY3JlYXRlIiwidGFza3MuZGVsZXRlIiwidGFza3MuZWRpdCIsInRhc2tzLnZpZXciLCJ1cmxzLmNyZWF0ZSIsInVybHMuZGVsZXRlIiwidXJscy5lZGl0IiwidXJscy52aWV3IiwidXNlcnMuY3JlYXRlIiwidXNlcnMuZGVsZXRlIiwidXNlcnMuZWRpdCIsInVzZXJzLnZpZXciXSwiZXhwIjoxNzY0MDA4NDAyLCJpc3MiOiJPbW5pUGxhbm5lciIsImF1ZCI6Ik9tbmlQbGFubmVyVXNlcnMifQ.ivveEf1eA81ipGAygtK-UJ1LEYRVrhdGIqbVHdGrlOY","refreshToken":"6t5j1kGNM9lKPThDzXEJdaHWdwZ9I08I7YWL0XRd3tSPu/l9adahK16XsqvpO8rph9Q/wkKbfayGIOkqODN47Q==","expiresAt":"2025-11-24T18:20:02.9019977Z","user":{"id":1,"email":"admin@omniplanner.com","username":"admin","first_name":"System","last_name":"Administrator","phone":null,"email_verified":true},"roles":["Super Admin"],"permissions":["budget.create","budget.delete","budget.edit","budget.view","categories.create","categories.delete","categories.edit","categories.view","credentials.create","credentials.delete","credentials.edit","credentials.view","notes.create","notes.delete","notes.edit","notes.view","permissions.manage","permissions.view","priorities.create","priorities.delete","priorities.edit","priorities.view","roles.create","roles.delete","roles.edit","roles.view","settings.manage","settings.view","statuses.create","statuses.delete","statuses.edit","statuses.view","tasks.create","tasks.delete","tasks.edit","tasks.view","urls.create","urls.delete","urls.edit","urls.view","users.create","users.delete","users.edit","users.view"]},"message":"Login successful","success":true}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22:50:06</x:t>
+    <x:t>11:52:07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"token":"eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1laWRlbnRpZmllciI6IjEiLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9lbWFpbGFkZHJlc3MiOiJhZG1pbkBvbW5pcGxhbm5lci5jb20iLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1lIjoiYWRtaW4iLCJqdGkiOiI3MDc0ZGM2NC1kODA3LTQ4YjMtYWNhMi02OGZkNzUyZWI4ZmUiLCJodHRwOi8vc2NoZW1hcy5taWNyb3NvZnQuY29tL3dzLzIwMDgvMDYvaWRlbnRpdHkvY2xhaW1zL3JvbGUiOiJTdXBlciBBZG1pbiIsInBlcm1pc3Npb24iOlsiYnVkZ2V0LmNyZWF0ZSIsImJ1ZGdldC5kZWxldGUiLCJidWRnZXQuZWRpdCIsImJ1ZGdldC52aWV3IiwiY2F0ZWdvcmllcy5jcmVhdGUiLCJjYXRlZ29yaWVzLmRlbGV0ZSIsImNhdGVnb3JpZXMuZWRpdCIsImNhdGVnb3JpZXMudmlldyIsImNyZWRlbnRpYWxzLmNyZWF0ZSIsImNyZWRlbnRpYWxzLmRlbGV0ZSIsImNyZWRlbnRpYWxzLmVkaXQiLCJjcmVkZW50aWFscy52aWV3Iiwibm90ZXMuY3JlYXRlIiwibm90ZXMuZGVsZXRlIiwibm90ZXMuZWRpdCIsIm5vdGVzLnZpZXciLCJwZXJtaXNzaW9ucy5tYW5hZ2UiLCJwZXJtaXNzaW9ucy52aWV3IiwicHJpb3JpdGllcy5jcmVhdGUiLCJwcmlvcml0aWVzLmRlbGV0ZSIsInByaW9yaXRpZXMuZWRpdCIsInByaW9yaXRpZXMudmlldyIsInJvbGVzLmNyZWF0ZSIsInJvbGVzLmRlbGV0ZSIsInJvbGVzLmVkaXQiLCJyb2xlcy52aWV3Iiwic2V0dGluZ3MubWFuYWdlIiwic2V0dGluZ3MudmlldyIsInN0YXR1c2VzLmNyZWF0ZSIsInN0YXR1c2VzLmRlbGV0ZSIsInN0YXR1c2VzLmVkaXQiLCJzdGF0dXNlcy52aWV3IiwidGFza3MuY3JlYXRlIiwidGFza3MuZGVsZXRlIiwidGFza3MuZWRpdCIsInRhc2tzLnZpZXciLCJ1cmxzLmNyZWF0ZSIsInVybHMuZGVsZXRlIiwidXJscy5lZGl0IiwidXJscy52aWV3IiwidXNlcnMuY3JlYXRlIiwidXNlcnMuZGVsZXRlIiwidXNlcnMuZWRpdCIsInVzZXJzLnZpZXciXSwiZXhwIjoxNzYzOTY4OTMzLCJpc3MiOiJPbW5pUGxhbm5lciIsImF1ZCI6Ik9tbmlQbGFubmVyVXNlcnMifQ.pY6QTbNXbk3jDg3b3fIq-EpdVCw9bMSrb3n8X0qbWqA","refreshToken":"xE5zCHKw+n+TYZ3Nol2NMUfcltDpNfVV4EjP5dVTuksCXToFYCVzOAStUg15o+6ZURyZLxUtL/eeAgLgpHHzIA==","expiresAt":"2025-11-24T07:22:14.0268616Z","user":{"id":1,"email":"admin@omniplanner.com","username":"admin","first_name":"System","last_name":"Administrator","phone":null,"email_verified":true},"roles":["Super Admin"],"permissions":["budget.create","budget.delete","budget.edit","budget.view","categories.create","categories.delete","categories.edit","categories.view","credentials.create","credentials.delete","credentials.edit","credentials.view","notes.create","notes.delete","notes.edit","notes.view","permissions.manage","permissions.view","priorities.create","priorities.delete","priorities.edit","priorities.view","roles.create","roles.delete","roles.edit","roles.view","settings.manage","settings.view","statuses.create","statuses.delete","statuses.edit","statuses.view","tasks.create","tasks.delete","tasks.edit","tasks.view","urls.create","urls.delete","urls.edit","urls.view","users.create","users.delete","users.edit","users.view"]},"message":"Login successful","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11:52:44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11:56:19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"title":"Add all tasks to production","description":null,"priority_level_id":1,"status_id":28,"category_id":38,"task_on_date":"2025-11-24","start_time":"00:00","end_time":"00:00","estimated_hours":1,"priority_order":null,"remarks":null,"url_ids":null,"important":false,"completed":false,"periodic_tasks_main_task_id":null}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":1,"title":"Add all tasks to production","description":null,"priority_level":{"name":"High","color":"#c70553"},"status":{"name":"In Progress","color":"#196bd7"},"category":{"name":"Personal","icon":"\uD83C\uDFAA"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:26:19.6487132Z","updatedAt":"2025-11-24T06:26:19.6499688Z","estimatedHours":null,"priority_order":null,"subtasks":[],"isExpanded":false,"remarks":null,"urls":[],"important":false,"completed":false,"periodic_task":null},"message":"Main task added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11:57:27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":1,"title":"Add tasks from baryons.net  - Tasks sheet","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":1,"title":"Add tasks from baryons.net  - Tasks sheet","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:27:27.9266293Z","updatedAt":"2025-11-24T06:27:27.9268691Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11:58:34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":1,"title":"Add tasks from baryons.net  - CT chrome tab","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":2,"title":"Add tasks from baryons.net  - CT chrome tab","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:28:34.9194114Z","updatedAt":"2025-11-24T06:28:34.9194121Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11:58:49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"id":1,"title":"Add tasks from baryons.net  - Tasks chrome tab","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":0,"priority_order":1,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":1,"title":"Add tasks from baryons.net  - Tasks chrome tab","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:28:49.9720614Z","updatedAt":"2025-11-24T06:28:49.972069Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask updated successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11:59:01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":1,"title":"Add tasks from baryons.net  - Pricing chrome tab","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":3,"title":"Add tasks from baryons.net  - Pricing chrome tab","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:29:01.8051167Z","updatedAt":"2025-11-24T06:29:01.8051177Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:01:11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":1,"title":"Add tasks from personal mail OmniPanner  - All excel sheets explore and add - if any tasks are there to be yet worked or need implementation in the OmniPlanner application then add them to the Omni Planner Pm Plan Task","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":4,"title":"Add tasks from personal mail OmniPanner  - All excel sheets explore and add - if any tasks are there to be yet worked or need implementation in the OmniPlanner application then add them to the Omni Planner Pm Plan Task","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:31:11.4169449Z","updatedAt":"2025-11-24T06:31:11.416946Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:15:44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":1,"title":"Add all tasks and things from notepad++ to omnplanner application","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":5,"title":"Add all tasks and things from notepad++ to omnplanner application","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:45:45.2334052Z","updatedAt":"2025-11-24T06:45:45.2334066Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:16:07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":1,"title":"Add all tasks and things from mobile notes app to omnplanner application","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":6,"title":"Add all tasks and things from mobile notes app to omnplanner application","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:46:07.7063662Z","updatedAt":"2025-11-24T06:46:07.7063667Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:16:25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":1,"title":"Add all tasks and things from chats to omniplanner application","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":7,"title":"Add all tasks and things from chats to omniplanner application","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:46:25.1299459Z","updatedAt":"2025-11-24T06:46:25.1299465Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:18:44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"title":"OmniPlanner Pm plan","description":"Pending tasks | next version items | track what level released to production","priority_level_id":2,"status_id":15,"category_id":38,"task_on_date":"2025-11-24","start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"remarks":null,"url_ids":null,"important":false,"completed":false,"periodic_tasks_main_task_id":null}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":2,"title":"OmniPlanner Pm plan","description":"Pending tasks | next version items | track what level released to production","priority_level":{"name":"Medium","color":"#d1b529"},"status":{"name":"Open","color":"#d1b529"},"category":{"name":"Personal","icon":"\uD83C\uDFAA"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:48:44.8473085Z","updatedAt":"2025-11-24T06:48:44.8473092Z","estimatedHours":null,"priority_order":null,"subtasks":[],"isExpanded":false,"remarks":null,"urls":[],"important":false,"completed":false,"periodic_task":null},"message":"Main task added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:20:47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":1,"title":"Move full system of mine to omniplanner app","description":"all drives things | chrome tabs | structure | work flow","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":8,"title":"Move full system of mine to omniplanner app","description":"all drives things | chrome tabs | structure | work flow","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:50:47.6914736Z","updatedAt":"2025-11-24T06:50:47.6914748Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:24:54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"title":"Safety tasks sheet ","description":null,"priority_level_id":2,"status_id":15,"category_id":38,"task_on_date":"2025-11-24","start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"remarks":"Maintain this sheet unless  application is fully trustable and tested. \nEach tasks added here should be added to the safety tasks sheet. ","url_ids":null,"important":false,"completed":false,"periodic_tasks_main_task_id":null}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":3,"title":"Safety tasks sheet ","description":null,"priority_level":{"name":"Medium","color":"#d1b529"},"status":{"name":"Open","color":"#d1b529"},"category":{"name":"Personal","icon":"\uD83C\uDFAA"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:54:54.6926741Z","updatedAt":"2025-11-24T06:54:54.692675Z","estimatedHours":null,"priority_order":null,"subtasks":[],"isExpanded":false,"remarks":"Maintain this sheet unless  application is fully trustable and tested. \nEach tasks added here should be added to the safety tasks sheet. ","urls":[],"important":false,"completed":false,"periodic_task":null},"message":"Main task added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:25:26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":3,"title":" Create a Safety task sheet and bind the URL to the main task","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":9,"title":" Create a Safety task sheet and bind the URL to the main task","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T06:55:26.9259035Z","updatedAt":"2025-11-24T06:55:26.9259042Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"3","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:30:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"id":3,"title":"Safety tasks sheet ","description":null,"priority_level_id":2,"status_id":15,"category_id":38,"task_on_date":null,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":3,"remarks":"Maintain this sheet unless  application is fully trustable and tested. \nEach tasks added here should be added to the safety tasks sheet. ","url_ids":null,"important":false,"completed":false,"periodic_tasks_main_task_id":null}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":3,"title":"Safety tasks sheet ","description":null,"priority_level":{"name":"Medium","color":"#d1b529"},"status":{"name":"Open","color":"#d1b529"},"category":{"name":"Personal","icon":"\uD83C\uDFAA"},"taskOnDate":null,"startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T12:24:54.665702","updatedAt":"2025-11-24T12:30:39.038011","estimatedHours":null,"priority_order":3,"subtasks":[{"id":9,"title":" Create a Safety task sheet and bind the URL to the main task","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T12:25:26.878404","updatedAt":"2025-11-24T12:25:26.878404","estimatedHours":null,"priority_order":1,"subtasks":[],"parentId":"3","level":1,"isExpanded":false,"completed":false,"important":false}],"isExpanded":false,"remarks":"Maintain this sheet unless  application is fully trustable and tested. \nEach tasks added here should be added to the safety tasks sheet. ","urls":[],"important":false,"completed":false,"periodic_task":null},"message":"Main task updated successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":1,"title":"Move crrdentials and links to omniplanner (grow bar yons email accessible)","description":"https://docs.google.com/document/d/1Hc51IDtf-32kY9M4SfS6SLdQUhdbgsJ-UvZ2ISSAeIM/edit?tab=t.0","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":10,"title":"Move crrdentials and links to omniplanner (grow bar yons email accessible)","description":"https://docs.google.com/document/d/1Hc51IDtf-32kY9M4SfS6SLdQUhdbgsJ-UvZ2ISSAeIM/edit?tab=t.0","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T07:04:51.4789435Z","updatedAt":"2025-11-24T07:04:51.4789457Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"1","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:47:04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"id":3,"title":"Safety tasks sheet ","description":"Instant | Daily | Paralley | Keep Update","priority_level_id":2,"status_id":15,"category_id":38,"task_on_date":null,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":3,"remarks":"Maintain this sheet unless  application is fully trustable and tested. \nEach tasks added here should be added to the safety tasks sheet. ","url_ids":null,"important":false,"completed":false,"periodic_tasks_main_task_id":null}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":3,"title":"Safety tasks sheet ","description":"Instant | Daily | Paralley | Keep Update","priority_level":{"name":"Medium","color":"#d1b529"},"status":{"name":"Open","color":"#d1b529"},"category":{"name":"Personal","icon":"\uD83C\uDFAA"},"taskOnDate":null,"startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T12:24:54.665702","updatedAt":"2025-11-24T12:47:04.576504","estimatedHours":null,"priority_order":3,"subtasks":[{"id":9,"title":" Create a Safety task sheet and bind the URL to the main task","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T12:25:26.878404","updatedAt":"2025-11-24T12:25:26.878404","estimatedHours":null,"priority_order":1,"subtasks":[],"parentId":"3","level":1,"isExpanded":false,"completed":false,"important":false}],"isExpanded":false,"remarks":"Maintain this sheet unless  application is fully trustable and tested. \nEach tasks added here should be added to the safety tasks sheet. ","urls":[],"important":false,"completed":false,"periodic_task":null},"message":"Main task updated successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:09:37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:09:40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"token":"eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1laWRlbnRpZmllciI6IjEiLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9lbWFpbGFkZHJlc3MiOiJhZG1pbkBvbW5pcGxhbm5lci5jb20iLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1lIjoiYWRtaW4iLCJqdGkiOiJjNTdlNWVhZi04OGYzLTRkZDktOTYyMi04MWEzOWZmZDY0ZjgiLCJodHRwOi8vc2NoZW1hcy5taWNyb3NvZnQuY29tL3dzLzIwMDgvMDYvaWRlbnRpdHkvY2xhaW1zL3JvbGUiOiJTdXBlciBBZG1pbiIsInBlcm1pc3Npb24iOlsiYnVkZ2V0LmNyZWF0ZSIsImJ1ZGdldC5kZWxldGUiLCJidWRnZXQuZWRpdCIsImJ1ZGdldC52aWV3IiwiY2F0ZWdvcmllcy5jcmVhdGUiLCJjYXRlZ29yaWVzLmRlbGV0ZSIsImNhdGVnb3JpZXMuZWRpdCIsImNhdGVnb3JpZXMudmlldyIsImNyZWRlbnRpYWxzLmNyZWF0ZSIsImNyZWRlbnRpYWxzLmRlbGV0ZSIsImNyZWRlbnRpYWxzLmVkaXQiLCJjcmVkZW50aWFscy52aWV3Iiwibm90ZXMuY3JlYXRlIiwibm90ZXMuZGVsZXRlIiwibm90ZXMuZWRpdCIsIm5vdGVzLnZpZXciLCJwZXJtaXNzaW9ucy5tYW5hZ2UiLCJwZXJtaXNzaW9ucy52aWV3IiwicHJpb3JpdGllcy5jcmVhdGUiLCJwcmlvcml0aWVzLmRlbGV0ZSIsInByaW9yaXRpZXMuZWRpdCIsInByaW9yaXRpZXMudmlldyIsInJvbGVzLmNyZWF0ZSIsInJvbGVzLmRlbGV0ZSIsInJvbGVzLmVkaXQiLCJyb2xlcy52aWV3Iiwic2V0dGluZ3MubWFuYWdlIiwic2V0dGluZ3MudmlldyIsInN0YXR1c2VzLmNyZWF0ZSIsInN0YXR1c2VzLmRlbGV0ZSIsInN0YXR1c2VzLmVkaXQiLCJzdGF0dXNlcy52aWV3IiwidGFza3MuY3JlYXRlIiwidGFza3MuZGVsZXRlIiwidGFza3MuZWRpdCIsInRhc2tzLnZpZXciLCJ1cmxzLmNyZWF0ZSIsInVybHMuZGVsZXRlIiwidXJscy5lZGl0IiwidXJscy52aWV3IiwidXNlcnMuY3JlYXRlIiwidXNlcnMuZGVsZXRlIiwidXNlcnMuZWRpdCIsInVzZXJzLnZpZXciXSwiZXhwIjoxNzYzOTczNTgwLCJpc3MiOiJPbW5pUGxhbm5lciIsImF1ZCI6Ik9tbmlQbGFubmVyVXNlcnMifQ.TgVDsSfWSJ1KSQSXLIa9pGou4_sUc9k2cvvvFYu4VJM","refreshToken":"cWfhl0C8ViTPR5eA+XECbbV84fQ0HvV60ndbvGeKp3/zGr3MpY3Qp80lF5Gb273ES/loE44dXm1nEL23G/NlgA==","expiresAt":"2025-11-24T08:39:40.1372196Z","user":{"id":1,"email":"admin@omniplanner.com","username":"admin","first_name":"System","last_name":"Administrator","phone":null,"email_verified":true},"roles":["Super Admin"],"permissions":["budget.create","budget.delete","budget.edit","budget.view","categories.create","categories.delete","categories.edit","categories.view","credentials.create","credentials.delete","credentials.edit","credentials.view","notes.create","notes.delete","notes.edit","notes.view","permissions.manage","permissions.view","priorities.create","priorities.delete","priorities.edit","priorities.view","roles.create","roles.delete","roles.edit","roles.view","settings.manage","settings.view","statuses.create","statuses.delete","statuses.edit","statuses.view","tasks.create","tasks.delete","tasks.edit","tasks.view","urls.create","urls.delete","urls.edit","urls.view","users.create","users.delete","users.edit","users.view"]},"message":"Login successful","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:09:42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:10:13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"title":"Baryons Timesheet","description":null,"priority_level_id":2,"status_id":15,"category_id":41,"task_on_date":null,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"remarks":null,"url_ids":null,"important":false,"completed":false,"periodic_tasks_main_task_id":null}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":4,"title":"Baryons Timesheet","description":null,"priority_level":{"name":"Medium","color":"#d1b529"},"status":{"name":"Open","color":"#d1b529"},"category":{"name":"Office &gt; System","icon":"\uD83D\uDCBC"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T07:40:13.8319865Z","updatedAt":"2025-11-24T07:40:13.8319877Z","estimatedHours":null,"priority_order":null,"subtasks":[],"isExpanded":false,"remarks":null,"urls":[],"important":false,"completed":false,"periodic_task":null},"message":"Main task added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:10:28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"id":3,"title":"Safety tasks sheet ","description":"Instant | Daily | Paralley | Keep Update","priority_level_id":2,"status_id":15,"category_id":38,"task_on_date":null,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"remarks":"Maintain this sheet unless  application is fully trustable and tested. \nEach tasks added here should be added to the safety tasks sheet. ","url_ids":null,"important":false,"completed":false,"periodic_tasks_main_task_id":null}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":3,"title":"Safety tasks sheet ","description":"Instant | Daily | Paralley | Keep Update","priority_level":{"name":"Medium","color":"#d1b529"},"status":{"name":"Open","color":"#d1b529"},"category":{"name":"Personal","icon":"\uD83C\uDFAA"},"taskOnDate":null,"startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T12:24:54.665702","updatedAt":"2025-11-24T13:10:28.308543","estimatedHours":null,"priority_order":null,"subtasks":[{"id":9,"title":" Create a Safety task sheet and bind the URL to the main task","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T12:25:26.878404","updatedAt":"2025-11-24T12:25:26.878404","estimatedHours":null,"priority_order":1,"subtasks":[],"parentId":"3","level":1,"isExpanded":false,"completed":false,"important":false}],"isExpanded":false,"remarks":"Maintain this sheet unless  application is fully trustable and tested. \nEach tasks added here should be added to the safety tasks sheet. ","urls":[],"important":false,"completed":false,"periodic_task":null},"message":"Main task updated successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:11:24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":4,"title":"Create a Timesheet and bind the URL to the main task","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":11,"title":"Create a Timesheet and bind the URL to the main task","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T07:41:24.6731172Z","updatedAt":"2025-11-24T07:41:24.6731184Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"4","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:12:40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"tasks_main_task_id":2,"title":"When the token gets expired - show session expired popup as in CT","description":"","priority_level_id":2,"status_id":15,"start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"important":false,"completed":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":12,"title":"When the token gets expired - show session expired popup as in CT","description":"","status":{"name":"Open","color":"#d1b529"},"priority_level":{"name":"Medium","color":"#d1b529"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T07:42:41.0509918Z","updatedAt":"2025-11-24T07:42:41.0509927Z","estimatedHours":null,"priority_order":null,"subtasks":[],"parentId":"2","level":1,"isExpanded":false,"completed":false,"important":false},"message":"Level 1 subtask added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:26:51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"title":"Omniplanner - need to setup production easy daily basis triggerable - need to create a compact unfied compiled build like setup - having front end backend and db ","description":null,"priority_level_id":2,"status_id":15,"category_id":38,"task_on_date":"2025-11-24","start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":null,"remarks":"a easy to trigger the application on a daily basis.\nlearn the ways of preparing compact builds for making live.","url_ids":null,"important":false,"completed":false,"periodic_tasks_main_task_id":null}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":5,"title":"Omniplanner - need to setup production easy daily basis triggerable - need to create a compact unfied compiled build like setup - having front end backend and db ","description":null,"priority_level":{"name":"Medium","color":"#d1b529"},"status":{"name":"Open","color":"#d1b529"},"category":{"name":"Personal","icon":"\uD83C\uDFAA"},"taskOnDate":null,"startTime":null,"endTime":null,"createdAt":"2025-11-24T07:56:52.1601992Z","updatedAt":"2025-11-24T07:56:52.1602012Z","estimatedHours":null,"priority_order":null,"subtasks":[],"isExpanded":false,"remarks":"a easy to trigger the application on a daily basis.\nlearn the ways of preparing compact builds for making live.","urls":[],"important":false,"completed":false,"periodic_task":null},"message":"Main task added successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:27:35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"id":5,"title":"Omniplanner - need easy daily basis triggerable production setup","description":"Omniplanner - need to setup production easy daily basis triggerable - need to create a compact unfied compiled build like setup - having front end backend and db ","priority_level_id":2,"status_id":15,"category_id":38,"task_on_date":"2025-11-24","start_time":"00:00","end_time":"00:00","estimated_hours":null,"priority_order":3,"remarks":"a easy to trigger the application on a daily basis.\nlearn the ways of preparing compact builds for making live.","url_ids":null,"important":false,"completed":false,"periodic_tasks_main_task_id":null}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"id":5,"title":"Omniplanner - need easy daily basis triggerable production setup","description":"Omniplanner - need to setup production easy daily basis triggerable - need to create a compact unfied compiled build like setup - having front end backend and db ","priority_level":{"name":"Medium","color":"#d1b529"},"status":{"name":"Open","color":"#d1b529"},"category":{"name":"Personal","icon":"\uD83C\uDFAA"},"taskOnDate":"2025-11-24T00:00:00","startTime":"00:00","endTime":"00:00","createdAt":"2025-11-24T13:26:51.933452","updatedAt":"2025-11-24T13:27:35.292508","estimatedHours":null,"priority_order":3,"subtasks":[],"isExpanded":false,"remarks":"a easy to trigger the application on a daily basis.\nlearn the ways of preparing compact builds for making live.","urls":[],"important":false,"completed":false,"periodic_task":null},"message":"Main task updated successfully","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22:48:05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"token":"eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1laWRlbnRpZmllciI6IjEiLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9lbWFpbGFkZHJlc3MiOiJhZG1pbkBvbW5pcGxhbm5lci5jb20iLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1lIjoiYWRtaW4iLCJqdGkiOiIxY2NmY2UzYS1kMDEyLTRhY2UtYmEwZS1lMmNkOWM3ZDM1NGIiLCJodHRwOi8vc2NoZW1hcy5taWNyb3NvZnQuY29tL3dzLzIwMDgvMDYvaWRlbnRpdHkvY2xhaW1zL3JvbGUiOiJTdXBlciBBZG1pbiIsInBlcm1pc3Npb24iOlsiYnVkZ2V0LmNyZWF0ZSIsImJ1ZGdldC5kZWxldGUiLCJidWRnZXQuZWRpdCIsImJ1ZGdldC52aWV3IiwiY2F0ZWdvcmllcy5jcmVhdGUiLCJjYXRlZ29yaWVzLmRlbGV0ZSIsImNhdGVnb3JpZXMuZWRpdCIsImNhdGVnb3JpZXMudmlldyIsImNyZWRlbnRpYWxzLmNyZWF0ZSIsImNyZWRlbnRpYWxzLmRlbGV0ZSIsImNyZWRlbnRpYWxzLmVkaXQiLCJjcmVkZW50aWFscy52aWV3Iiwibm90ZXMuY3JlYXRlIiwibm90ZXMuZGVsZXRlIiwibm90ZXMuZWRpdCIsIm5vdGVzLnZpZXciLCJwZXJtaXNzaW9ucy5tYW5hZ2UiLCJwZXJtaXNzaW9ucy52aWV3IiwicHJpb3JpdGllcy5jcmVhdGUiLCJwcmlvcml0aWVzLmRlbGV0ZSIsInByaW9yaXRpZXMuZWRpdCIsInByaW9yaXRpZXMudmlldyIsInJvbGVzLmNyZWF0ZSIsInJvbGVzLmRlbGV0ZSIsInJvbGVzLmVkaXQiLCJyb2xlcy52aWV3Iiwic2V0dGluZ3MubWFuYWdlIiwic2V0dGluZ3MudmlldyIsInN0YXR1c2VzLmNyZWF0ZSIsInN0YXR1c2VzLmRlbGV0ZSIsInN0YXR1c2VzLmVkaXQiLCJzdGF0dXNlcy52aWV3IiwidGFza3MuY3JlYXRlIiwidGFza3MuZGVsZXRlIiwidGFza3MuZWRpdCIsInRhc2tzLnZpZXciLCJ1cmxzLmNyZWF0ZSIsInVybHMuZGVsZXRlIiwidXJscy5lZGl0IiwidXJscy52aWV3IiwidXNlcnMuY3JlYXRlIiwidXNlcnMuZGVsZXRlIiwidXNlcnMuZWRpdCIsInVzZXJzLnZpZXciXSwiZXhwIjoxNzY0MDA4Mjk1LCJpc3MiOiJPbW5pUGxhbm5lciIsImF1ZCI6Ik9tbmlQbGFubmVyVXNlcnMifQ.OaIX-tJb7EsVjeJUGTIUeYWUyiEi0IX9Jnov_CRh92k","refreshToken":"p9bFUwsyDAN1mDuOzF5lq2Y4DbJDS32ygy9cfb9KIIKXBzKTW1yFA055tR7jzUTBFaNqtB+U+ZJhUjZA/7o+8w==","expiresAt":"2025-11-24T18:18:15.6830443Z","user":{"id":1,"email":"admin@omniplanner.com","username":"admin","first_name":"System","last_name":"Administrator","phone":null,"email_verified":true},"roles":["Super Admin"],"permissions":["budget.create","budget.delete","budget.edit","budget.view","categories.create","categories.delete","categories.edit","categories.view","credentials.create","credentials.delete","credentials.edit","credentials.view","notes.create","notes.delete","notes.edit","notes.view","permissions.manage","permissions.view","priorities.create","priorities.delete","priorities.edit","priorities.view","roles.create","roles.delete","roles.edit","roles.view","settings.manage","settings.view","statuses.create","statuses.delete","statuses.edit","statuses.view","tasks.create","tasks.delete","tasks.edit","tasks.view","urls.create","urls.delete","urls.edit","urls.view","users.create","users.delete","users.edit","users.view"]},"message":"Login successful","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22:49:08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22:49:48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22:49:55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"token":"eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1laWRlbnRpZmllciI6IjEiLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9lbWFpbGFkZHJlc3MiOiJhZG1pbkBvbW5pcGxhbm5lci5jb20iLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1lIjoiYWRtaW4iLCJqdGkiOiJlOWQ1OGUwOC1iNmQ5LTQ3YzQtYjQzNi1hN2Q0NmU4ZGY0NzIiLCJodHRwOi8vc2NoZW1hcy5taWNyb3NvZnQuY29tL3dzLzIwMDgvMDYvaWRlbnRpdHkvY2xhaW1zL3JvbGUiOiJTdXBlciBBZG1pbiIsInBlcm1pc3Npb24iOlsiYnVkZ2V0LmNyZWF0ZSIsImJ1ZGdldC5kZWxldGUiLCJidWRnZXQuZWRpdCIsImJ1ZGdldC52aWV3IiwiY2F0ZWdvcmllcy5jcmVhdGUiLCJjYXRlZ29yaWVzLmRlbGV0ZSIsImNhdGVnb3JpZXMuZWRpdCIsImNhdGVnb3JpZXMudmlldyIsImNyZWRlbnRpYWxzLmNyZWF0ZSIsImNyZWRlbnRpYWxzLmRlbGV0ZSIsImNyZWRlbnRpYWxzLmVkaXQiLCJjcmVkZW50aWFscy52aWV3Iiwibm90ZXMuY3JlYXRlIiwibm90ZXMuZGVsZXRlIiwibm90ZXMuZWRpdCIsIm5vdGVzLnZpZXciLCJwZXJtaXNzaW9ucy5tYW5hZ2UiLCJwZXJtaXNzaW9ucy52aWV3IiwicHJpb3JpdGllcy5jcmVhdGUiLCJwcmlvcml0aWVzLmRlbGV0ZSIsInByaW9yaXRpZXMuZWRpdCIsInByaW9yaXRpZXMudmlldyIsInJvbGVzLmNyZWF0ZSIsInJvbGVzLmRlbGV0ZSIsInJvbGVzLmVkaXQiLCJyb2xlcy52aWV3Iiwic2V0dGluZ3MubWFuYWdlIiwic2V0dGluZ3MudmlldyIsInN0YXR1c2VzLmNyZWF0ZSIsInN0YXR1c2VzLmRlbGV0ZSIsInN0YXR1c2VzLmVkaXQiLCJzdGF0dXNlcy52aWV3IiwidGFza3MuY3JlYXRlIiwidGFza3MuZGVsZXRlIiwidGFza3MuZWRpdCIsInRhc2tzLnZpZXciLCJ1cmxzLmNyZWF0ZSIsInVybHMuZGVsZXRlIiwidXJscy5lZGl0IiwidXJscy52aWV3IiwidXNlcnMuY3JlYXRlIiwidXNlcnMuZGVsZXRlIiwidXNlcnMuZWRpdCIsInVzZXJzLnZpZXciXSwiZXhwIjoxNzY0MDA4Mzk2LCJpc3MiOiJPbW5pUGxhbm5lciIsImF1ZCI6Ik9tbmlQbGFubmVyVXNlcnMifQ.KpMY8ftjt5Tv5Gkg95aI5LrI0IL7E7SqFZi2YJMiPk4","refreshToken":"GEqfcO32HJ6zLdsHpoJgL5MQWwsoLoVanIt8GWuwHwQodmRE7Gc1AHnEmTYPqNYHcQRMbgULbueHqZo4dDF0qw==","expiresAt":"2025-11-24T18:19:56.3503949Z","user":{"id":1,"email":"admin@omniplanner.com","username":"admin","first_name":"System","last_name":"Administrator","phone":null,"email_verified":true},"roles":["Super Admin"],"permissions":["budget.create","budget.delete","budget.edit","budget.view","categories.create","categories.delete","categories.edit","categories.view","credentials.create","credentials.delete","credentials.edit","credentials.view","notes.create","notes.delete","notes.edit","notes.view","permissions.manage","permissions.view","priorities.create","priorities.delete","priorities.edit","priorities.view","roles.create","roles.delete","roles.edit","roles.view","settings.manage","settings.view","statuses.create","statuses.delete","statuses.edit","statuses.view","tasks.create","tasks.delete","tasks.edit","tasks.view","urls.create","urls.delete","urls.edit","urls.view","users.create","users.delete","users.edit","users.view"]},"message":"Login successful","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22:49:59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-11-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01:26:09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"data":{"token":"eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1laWRlbnRpZmllciI6IjEiLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9lbWFpbGFkZHJlc3MiOiJhZG1pbkBvbW5pcGxhbm5lci5jb20iLCJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1lIjoiYWRtaW4iLCJqdGkiOiI1N2I3MTBiMC0xMjA5LTRhNmItYmQzOC02YmY4MmRhZTFlYjciLCJodHRwOi8vc2NoZW1hcy5taWNyb3NvZnQuY29tL3dzLzIwMDgvMDYvaWRlbnRpdHkvY2xhaW1zL3JvbGUiOiJTdXBlciBBZG1pbiIsInBlcm1pc3Npb24iOlsiYnVkZ2V0LmNyZWF0ZSIsImJ1ZGdldC5kZWxldGUiLCJidWRnZXQuZWRpdCIsImJ1ZGdldC52aWV3IiwiY2F0ZWdvcmllcy5jcmVhdGUiLCJjYXRlZ29yaWVzLmRlbGV0ZSIsImNhdGVnb3JpZXMuZWRpdCIsImNhdGVnb3JpZXMudmlldyIsImNyZWRlbnRpYWxzLmNyZWF0ZSIsImNyZWRlbnRpYWxzLmRlbGV0ZSIsImNyZWRlbnRpYWxzLmVkaXQiLCJjcmVkZW50aWFscy52aWV3Iiwibm90ZXMuY3JlYXRlIiwibm90ZXMuZGVsZXRlIiwibm90ZXMuZWRpdCIsIm5vdGVzLnZpZXciLCJwZXJtaXNzaW9ucy5tYW5hZ2UiLCJwZXJtaXNzaW9ucy52aWV3IiwicHJpb3JpdGllcy5jcmVhdGUiLCJwcmlvcml0aWVzLmRlbGV0ZSIsInByaW9yaXRpZXMuZWRpdCIsInByaW9yaXRpZXMudmlldyIsInJvbGVzLmNyZWF0ZSIsInJvbGVzLmRlbGV0ZSIsInJvbGVzLmVkaXQiLCJyb2xlcy52aWV3Iiwic2V0dGluZ3MubWFuYWdlIiwic2V0dGluZ3MudmlldyIsInN0YXR1c2VzLmNyZWF0ZSIsInN0YXR1c2VzLmRlbGV0ZSIsInN0YXR1c2VzLmVkaXQiLCJzdGF0dXNlcy52aWV3IiwidGFza3MuY3JlYXRlIiwidGFza3MuZGVsZXRlIiwidGFza3MuZWRpdCIsInRhc2tzLnZpZXciLCJ1cmxzLmNyZWF0ZSIsInVybHMuZGVsZXRlIiwidXJscy5lZGl0IiwidXJscy52aWV3IiwidXNlcnMuY3JlYXRlIiwidXNlcnMuZGVsZXRlIiwidXNlcnMuZWRpdCIsInVzZXJzLnZpZXciXSwiZXhwIjoxNzY0MDE3NzcxLCJpc3MiOiJPbW5pUGxhbm5lciIsImF1ZCI6Ik9tbmlQbGFubmVyVXNlcnMifQ.rytzCuAhrddDZA93blois7PaS2DfrOncvRJ7qbBrxIk","refreshToken":"+6UyEUp/pIH0uFQL70wJqZ6O598fU8wtrYfz76CAyFQ1x+jw2dOyyBCCWJyYLOAGmAqMqe4HJfKQTNpRAR68qg==","expiresAt":"2025-11-24T20:56:11.1332036Z","user":{"id":1,"email":"admin@omniplanner.com","username":"admin","first_name":"System","last_name":"Administrator","phone":null,"email_verified":true},"roles":["Super Admin"],"permissions":["budget.create","budget.delete","budget.edit","budget.view","categories.create","categories.delete","categories.edit","categories.view","credentials.create","credentials.delete","credentials.edit","credentials.view","notes.create","notes.delete","notes.edit","notes.view","permissions.manage","permissions.view","priorities.create","priorities.delete","priorities.edit","priorities.view","roles.create","roles.delete","roles.edit","roles.view","settings.manage","settings.view","statuses.create","statuses.delete","statuses.edit","statuses.view","tasks.create","tasks.delete","tasks.edit","tasks.view","urls.create","urls.delete","urls.edit","urls.view","users.create","users.delete","users.edit","users.view"]},"message":"Login successful","success":true}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01:26:19</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -31450,16 +31681,16 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="E1010" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="F1010" s="0" t="s">
         <x:v>2078</x:v>
       </x:c>
-      <x:c r="F1010" s="0" t="s">
-        <x:v>352</x:v>
-      </x:c>
       <x:c r="G1010" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H1010" s="0" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="1011" spans="1:8">
@@ -31470,19 +31701,16 @@
         <x:v>2079</x:v>
       </x:c>
       <x:c r="C1011" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D1011" s="0" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="E1011" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F1011" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="G1011" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="H1011" s="0" t="b">
         <x:v>0</x:v>
@@ -31499,16 +31727,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D1012" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="E1012" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>2081</x:v>
       </x:c>
       <x:c r="F1012" s="0" t="s">
-        <x:v>2081</x:v>
+        <x:v>2082</x:v>
       </x:c>
       <x:c r="G1012" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="H1012" s="0" t="b">
         <x:v>1</x:v>
@@ -31519,21 +31747,792 @@
         <x:v>1954</x:v>
       </x:c>
       <x:c r="B1013" s="0" t="s">
-        <x:v>2082</x:v>
+        <x:v>2083</x:v>
       </x:c>
       <x:c r="C1013" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D1013" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1013" s="0" t="s">
+        <x:v>2084</x:v>
+      </x:c>
+      <x:c r="F1013" s="0" t="s">
+        <x:v>2085</x:v>
+      </x:c>
+      <x:c r="G1013" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1013" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1014" spans="1:8">
+      <x:c r="A1014" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1014" s="0" t="s">
+        <x:v>2086</x:v>
+      </x:c>
+      <x:c r="C1014" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1014" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1014" s="0" t="s">
+        <x:v>2087</x:v>
+      </x:c>
+      <x:c r="F1014" s="0" t="s">
+        <x:v>2088</x:v>
+      </x:c>
+      <x:c r="G1014" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1014" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1015" spans="1:8">
+      <x:c r="A1015" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1015" s="0" t="s">
+        <x:v>2089</x:v>
+      </x:c>
+      <x:c r="C1015" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D1015" s="0" t="s">
+        <x:v>965</x:v>
+      </x:c>
+      <x:c r="E1015" s="0" t="s">
+        <x:v>2090</x:v>
+      </x:c>
+      <x:c r="F1015" s="0" t="s">
+        <x:v>2091</x:v>
+      </x:c>
+      <x:c r="G1015" s="0" t="s">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="H1015" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1016" spans="1:8">
+      <x:c r="A1016" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1016" s="0" t="s">
+        <x:v>2092</x:v>
+      </x:c>
+      <x:c r="C1016" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1016" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1016" s="0" t="s">
+        <x:v>2093</x:v>
+      </x:c>
+      <x:c r="F1016" s="0" t="s">
+        <x:v>2094</x:v>
+      </x:c>
+      <x:c r="G1016" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1016" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1017" spans="1:8">
+      <x:c r="A1017" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1017" s="0" t="s">
+        <x:v>2095</x:v>
+      </x:c>
+      <x:c r="C1017" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1017" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1017" s="0" t="s">
+        <x:v>2096</x:v>
+      </x:c>
+      <x:c r="F1017" s="0" t="s">
+        <x:v>2097</x:v>
+      </x:c>
+      <x:c r="G1017" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1017" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1018" spans="1:8">
+      <x:c r="A1018" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1018" s="0" t="s">
+        <x:v>2098</x:v>
+      </x:c>
+      <x:c r="C1018" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1018" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1018" s="0" t="s">
+        <x:v>2099</x:v>
+      </x:c>
+      <x:c r="F1018" s="0" t="s">
+        <x:v>2100</x:v>
+      </x:c>
+      <x:c r="G1018" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1018" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1019" spans="1:8">
+      <x:c r="A1019" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1019" s="0" t="s">
+        <x:v>2101</x:v>
+      </x:c>
+      <x:c r="C1019" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1019" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1019" s="0" t="s">
+        <x:v>2102</x:v>
+      </x:c>
+      <x:c r="F1019" s="0" t="s">
+        <x:v>2103</x:v>
+      </x:c>
+      <x:c r="G1019" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1019" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1020" spans="1:8">
+      <x:c r="A1020" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1020" s="0" t="s">
+        <x:v>2104</x:v>
+      </x:c>
+      <x:c r="C1020" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1020" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1020" s="0" t="s">
+        <x:v>2105</x:v>
+      </x:c>
+      <x:c r="F1020" s="0" t="s">
+        <x:v>2106</x:v>
+      </x:c>
+      <x:c r="G1020" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1020" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1021" spans="1:8">
+      <x:c r="A1021" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1021" s="0" t="s">
+        <x:v>2107</x:v>
+      </x:c>
+      <x:c r="C1021" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1021" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="E1021" s="0" t="s">
+        <x:v>2108</x:v>
+      </x:c>
+      <x:c r="F1021" s="0" t="s">
+        <x:v>2109</x:v>
+      </x:c>
+      <x:c r="G1021" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="H1021" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1022" spans="1:8">
+      <x:c r="A1022" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1022" s="0" t="s">
+        <x:v>2110</x:v>
+      </x:c>
+      <x:c r="C1022" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1022" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1022" s="0" t="s">
+        <x:v>2111</x:v>
+      </x:c>
+      <x:c r="F1022" s="0" t="s">
+        <x:v>2112</x:v>
+      </x:c>
+      <x:c r="G1022" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1022" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1023" spans="1:8">
+      <x:c r="A1023" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1023" s="0" t="s">
+        <x:v>2113</x:v>
+      </x:c>
+      <x:c r="C1023" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1023" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="E1023" s="0" t="s">
+        <x:v>2114</x:v>
+      </x:c>
+      <x:c r="F1023" s="0" t="s">
+        <x:v>2115</x:v>
+      </x:c>
+      <x:c r="G1023" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="H1023" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1024" spans="1:8">
+      <x:c r="A1024" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1024" s="0" t="s">
+        <x:v>2116</x:v>
+      </x:c>
+      <x:c r="C1024" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1024" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1024" s="0" t="s">
+        <x:v>2117</x:v>
+      </x:c>
+      <x:c r="F1024" s="0" t="s">
+        <x:v>2118</x:v>
+      </x:c>
+      <x:c r="G1024" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1024" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1025" spans="1:8">
+      <x:c r="A1025" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1025" s="0" t="s">
+        <x:v>2119</x:v>
+      </x:c>
+      <x:c r="C1025" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D1025" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="E1025" s="0" t="s">
+        <x:v>2120</x:v>
+      </x:c>
+      <x:c r="F1025" s="0" t="s">
+        <x:v>2121</x:v>
+      </x:c>
+      <x:c r="G1025" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="H1025" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1026" spans="1:8">
+      <x:c r="A1026" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1026" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C1026" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1026" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1026" s="0" t="s">
+        <x:v>2122</x:v>
+      </x:c>
+      <x:c r="F1026" s="0" t="s">
+        <x:v>2123</x:v>
+      </x:c>
+      <x:c r="G1026" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1026" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1027" spans="1:8">
+      <x:c r="A1027" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1027" s="0" t="s">
+        <x:v>2124</x:v>
+      </x:c>
+      <x:c r="C1027" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D1027" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="E1027" s="0" t="s">
+        <x:v>2125</x:v>
+      </x:c>
+      <x:c r="F1027" s="0" t="s">
+        <x:v>2126</x:v>
+      </x:c>
+      <x:c r="G1027" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="H1027" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1028" spans="1:8">
+      <x:c r="A1028" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1028" s="0" t="s">
+        <x:v>2127</x:v>
+      </x:c>
+      <x:c r="C1028" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1028" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="E1028" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="F1028" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="G1028" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="H1028" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1029" spans="1:8">
+      <x:c r="A1029" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1029" s="0" t="s">
+        <x:v>2128</x:v>
+      </x:c>
+      <x:c r="C1029" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1029" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="E1029" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="F1029" s="0" t="s">
+        <x:v>2129</x:v>
+      </x:c>
+      <x:c r="G1029" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H1029" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1030" spans="1:8">
+      <x:c r="A1030" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1030" s="0" t="s">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="C1030" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D1030" s="0" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="F1013" s="0" t="s">
+      <x:c r="F1030" s="0" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="G1013" s="0" t="s">
+      <x:c r="G1030" s="0" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="H1013" s="0" t="b">
+      <x:c r="H1030" s="0" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1031" spans="1:8">
+      <x:c r="A1031" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1031" s="0" t="s">
+        <x:v>2131</x:v>
+      </x:c>
+      <x:c r="C1031" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1031" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="E1031" s="0" t="s">
+        <x:v>2132</x:v>
+      </x:c>
+      <x:c r="F1031" s="0" t="s">
+        <x:v>2133</x:v>
+      </x:c>
+      <x:c r="G1031" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="H1031" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1032" spans="1:8">
+      <x:c r="A1032" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1032" s="0" t="s">
+        <x:v>2134</x:v>
+      </x:c>
+      <x:c r="C1032" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D1032" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="E1032" s="0" t="s">
+        <x:v>2135</x:v>
+      </x:c>
+      <x:c r="F1032" s="0" t="s">
+        <x:v>2136</x:v>
+      </x:c>
+      <x:c r="G1032" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="H1032" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1033" spans="1:8">
+      <x:c r="A1033" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1033" s="0" t="s">
+        <x:v>2137</x:v>
+      </x:c>
+      <x:c r="C1033" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1033" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1033" s="0" t="s">
+        <x:v>2138</x:v>
+      </x:c>
+      <x:c r="F1033" s="0" t="s">
+        <x:v>2139</x:v>
+      </x:c>
+      <x:c r="G1033" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1033" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1034" spans="1:8">
+      <x:c r="A1034" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1034" s="0" t="s">
+        <x:v>2140</x:v>
+      </x:c>
+      <x:c r="C1034" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1034" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="E1034" s="0" t="s">
+        <x:v>2141</x:v>
+      </x:c>
+      <x:c r="F1034" s="0" t="s">
+        <x:v>2142</x:v>
+      </x:c>
+      <x:c r="G1034" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="H1034" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1035" spans="1:8">
+      <x:c r="A1035" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1035" s="0" t="s">
+        <x:v>2143</x:v>
+      </x:c>
+      <x:c r="C1035" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1035" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="E1035" s="0" t="s">
+        <x:v>2144</x:v>
+      </x:c>
+      <x:c r="F1035" s="0" t="s">
+        <x:v>2145</x:v>
+      </x:c>
+      <x:c r="G1035" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="H1035" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1036" spans="1:8">
+      <x:c r="A1036" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1036" s="0" t="s">
+        <x:v>2146</x:v>
+      </x:c>
+      <x:c r="C1036" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D1036" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="E1036" s="0" t="s">
+        <x:v>2147</x:v>
+      </x:c>
+      <x:c r="F1036" s="0" t="s">
+        <x:v>2148</x:v>
+      </x:c>
+      <x:c r="G1036" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="H1036" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1037" spans="1:8">
+      <x:c r="A1037" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1037" s="0" t="s">
+        <x:v>2149</x:v>
+      </x:c>
+      <x:c r="C1037" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1037" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="E1037" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="F1037" s="0" t="s">
+        <x:v>2150</x:v>
+      </x:c>
+      <x:c r="G1037" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H1037" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1038" spans="1:8">
+      <x:c r="A1038" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1038" s="0" t="s">
+        <x:v>2151</x:v>
+      </x:c>
+      <x:c r="C1038" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D1038" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F1038" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G1038" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H1038" s="0" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1039" spans="1:8">
+      <x:c r="A1039" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1039" s="0" t="s">
+        <x:v>2152</x:v>
+      </x:c>
+      <x:c r="C1039" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1039" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="E1039" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="F1039" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="G1039" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="H1039" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1040" spans="1:8">
+      <x:c r="A1040" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1040" s="0" t="s">
+        <x:v>2153</x:v>
+      </x:c>
+      <x:c r="C1040" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1040" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="E1040" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="F1040" s="0" t="s">
+        <x:v>2154</x:v>
+      </x:c>
+      <x:c r="G1040" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H1040" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1041" spans="1:8">
+      <x:c r="A1041" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
+      <x:c r="B1041" s="0" t="s">
+        <x:v>2155</x:v>
+      </x:c>
+      <x:c r="C1041" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D1041" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F1041" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G1041" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H1041" s="0" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1042" spans="1:8">
+      <x:c r="A1042" s="0" t="s">
+        <x:v>2156</x:v>
+      </x:c>
+      <x:c r="B1042" s="0" t="s">
+        <x:v>2157</x:v>
+      </x:c>
+      <x:c r="C1042" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D1042" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="E1042" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="F1042" s="0" t="s">
+        <x:v>2158</x:v>
+      </x:c>
+      <x:c r="G1042" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H1042" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1043" spans="1:8">
+      <x:c r="A1043" s="0" t="s">
+        <x:v>2156</x:v>
+      </x:c>
+      <x:c r="B1043" s="0" t="s">
+        <x:v>2159</x:v>
+      </x:c>
+      <x:c r="C1043" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D1043" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F1043" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G1043" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H1043" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
